--- a/XLibur.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
+++ b/XLibur.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
@@ -428,14 +428,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="30.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -486,136 +483,136 @@
       <x:c r="A2" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>-15</x:v>
       </x:c>
-      <x:c r="E2" s="0">
+      <x:c r="E2">
         <x:v>-19</x:v>
       </x:c>
-      <x:c r="F2" s="0">
+      <x:c r="F2">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="G2" s="0">
+      <x:c r="G2">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H2" s="0">
+      <x:c r="H2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="0">
+      <x:c r="I2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J2" s="0">
+      <x:c r="J2">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="K2" s="0">
+      <x:c r="K2">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="L2" s="0">
+      <x:c r="L2">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="M2" s="0">
+      <x:c r="M2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="N2" s="0">
+      <x:c r="N2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O2" s="0">
+      <x:c r="O2">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="P2" s="0">
+      <x:c r="P2">
         <x:v>-6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
       <x:c r="A3" s="1"/>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>-23</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>-29</x:v>
       </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="F3">
         <x:v>-8</x:v>
       </x:c>
-      <x:c r="G3" s="0">
+      <x:c r="G3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H3" s="0">
+      <x:c r="H3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I3" s="0">
+      <x:c r="I3">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J3" s="0">
+      <x:c r="J3">
         <x:v>-16</x:v>
       </x:c>
-      <x:c r="K3" s="0">
+      <x:c r="K3">
         <x:v>-30</x:v>
       </x:c>
-      <x:c r="L3" s="0">
+      <x:c r="L3">
         <x:v>-16</x:v>
       </x:c>
-      <x:c r="M3" s="0">
+      <x:c r="M3">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="N3" s="0">
+      <x:c r="N3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O3" s="0">
+      <x:c r="O3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P3" s="0">
+      <x:c r="P3">
         <x:v>-9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
       <x:c r="A4" s="1"/>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>-30</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="G4" s="0">
+      <x:c r="G4">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H4" s="0">
+      <x:c r="H4">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I4" s="0">
+      <x:c r="I4">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J4" s="0">
+      <x:c r="J4">
         <x:v>-22</x:v>
       </x:c>
-      <x:c r="K4" s="0">
+      <x:c r="K4">
         <x:v>-40</x:v>
       </x:c>
-      <x:c r="L4" s="0">
+      <x:c r="L4">
         <x:v>-21</x:v>
       </x:c>
-      <x:c r="M4" s="0">
+      <x:c r="M4">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="N4" s="0">
+      <x:c r="N4">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="O4" s="0">
+      <x:c r="O4">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P4" s="0">
+      <x:c r="P4">
         <x:v>-12</x:v>
       </x:c>
     </x:row>
@@ -623,136 +620,136 @@
       <x:c r="A5" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>-14</x:v>
       </x:c>
-      <x:c r="G5" s="0">
+      <x:c r="G5">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H5" s="0">
+      <x:c r="H5">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="I5" s="0">
+      <x:c r="I5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J5" s="0">
+      <x:c r="J5">
         <x:v>-27</x:v>
       </x:c>
-      <x:c r="K5" s="0">
+      <x:c r="K5">
         <x:v>-50</x:v>
       </x:c>
-      <x:c r="L5" s="0">
+      <x:c r="L5">
         <x:v>-27</x:v>
       </x:c>
-      <x:c r="M5" s="0">
+      <x:c r="M5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="N5" s="0">
+      <x:c r="N5">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="O5" s="0">
+      <x:c r="O5">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="P5" s="0">
+      <x:c r="P5">
         <x:v>-14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
       <x:c r="A6" s="1"/>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>-45</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>-58</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F6">
         <x:v>-17</x:v>
       </x:c>
-      <x:c r="G6" s="0">
+      <x:c r="G6">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H6" s="0">
+      <x:c r="H6">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I6" s="0">
+      <x:c r="I6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J6" s="0">
+      <x:c r="J6">
         <x:v>-33</x:v>
       </x:c>
-      <x:c r="K6" s="0">
+      <x:c r="K6">
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="L6" s="0">
+      <x:c r="L6">
         <x:v>-32</x:v>
       </x:c>
-      <x:c r="M6" s="0">
+      <x:c r="M6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="N6" s="0">
+      <x:c r="N6">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="O6" s="0">
+      <x:c r="O6">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="P6" s="0">
+      <x:c r="P6">
         <x:v>-17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
       <x:c r="A7" s="1"/>
-      <x:c r="C7" s="0">
+      <x:c r="C7">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="0">
+      <x:c r="D7">
         <x:v>-53</x:v>
       </x:c>
-      <x:c r="E7" s="0">
+      <x:c r="E7">
         <x:v>-67</x:v>
       </x:c>
-      <x:c r="F7" s="0">
+      <x:c r="F7">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="G7" s="0">
+      <x:c r="G7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H7" s="0">
+      <x:c r="H7">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="I7" s="0">
+      <x:c r="I7">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J7" s="0">
+      <x:c r="J7">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="K7" s="0">
+      <x:c r="K7">
         <x:v>-70</x:v>
       </x:c>
-      <x:c r="L7" s="0">
+      <x:c r="L7">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="M7" s="0">
+      <x:c r="M7">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="N7" s="0">
+      <x:c r="N7">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="O7" s="0">
+      <x:c r="O7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="P7" s="0">
+      <x:c r="P7">
         <x:v>-20</x:v>
       </x:c>
     </x:row>
@@ -760,136 +757,136 @@
       <x:c r="A8" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="0">
+      <x:c r="C8">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D8" s="0">
+      <x:c r="D8">
         <x:v>-61</x:v>
       </x:c>
-      <x:c r="E8" s="0">
+      <x:c r="E8">
         <x:v>-77</x:v>
       </x:c>
-      <x:c r="F8" s="0">
+      <x:c r="F8">
         <x:v>-22</x:v>
       </x:c>
-      <x:c r="G8" s="0">
+      <x:c r="G8">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H8" s="0">
+      <x:c r="H8">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="I8" s="0">
+      <x:c r="I8">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="J8" s="0">
+      <x:c r="J8">
         <x:v>-44</x:v>
       </x:c>
-      <x:c r="K8" s="0">
+      <x:c r="K8">
         <x:v>-80</x:v>
       </x:c>
-      <x:c r="L8" s="0">
+      <x:c r="L8">
         <x:v>-43</x:v>
       </x:c>
-      <x:c r="M8" s="0">
+      <x:c r="M8">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="N8" s="0">
+      <x:c r="N8">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="O8" s="0">
+      <x:c r="O8">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="P8" s="0">
+      <x:c r="P8">
         <x:v>-23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
       <x:c r="A9" s="1"/>
-      <x:c r="C9" s="0">
+      <x:c r="C9">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D9" s="0">
+      <x:c r="D9">
         <x:v>-68</x:v>
       </x:c>
-      <x:c r="E9" s="0">
+      <x:c r="E9">
         <x:v>-86</x:v>
       </x:c>
-      <x:c r="F9" s="0">
+      <x:c r="F9">
         <x:v>-25</x:v>
       </x:c>
-      <x:c r="G9" s="0">
+      <x:c r="G9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H9" s="0">
+      <x:c r="H9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="I9" s="0">
+      <x:c r="I9">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J9" s="0">
+      <x:c r="J9">
         <x:v>-49</x:v>
       </x:c>
-      <x:c r="K9" s="0">
+      <x:c r="K9">
         <x:v>-90</x:v>
       </x:c>
-      <x:c r="L9" s="0">
+      <x:c r="L9">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="M9" s="0">
+      <x:c r="M9">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="N9" s="0">
+      <x:c r="N9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="O9" s="0">
+      <x:c r="O9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="P9" s="0">
+      <x:c r="P9">
         <x:v>-26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
       <x:c r="A10" s="1"/>
-      <x:c r="C10" s="0">
+      <x:c r="C10">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="0">
+      <x:c r="D10">
         <x:v>-76</x:v>
       </x:c>
-      <x:c r="E10" s="0">
+      <x:c r="E10">
         <x:v>-96</x:v>
       </x:c>
-      <x:c r="F10" s="0">
+      <x:c r="F10">
         <x:v>-28</x:v>
       </x:c>
-      <x:c r="G10" s="0">
+      <x:c r="G10">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H10" s="0">
+      <x:c r="H10">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="I10" s="0">
+      <x:c r="I10">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J10" s="0">
+      <x:c r="J10">
         <x:v>-54</x:v>
       </x:c>
-      <x:c r="K10" s="0">
+      <x:c r="K10">
         <x:v>-100</x:v>
       </x:c>
-      <x:c r="L10" s="0">
+      <x:c r="L10">
         <x:v>-54</x:v>
       </x:c>
-      <x:c r="M10" s="0">
+      <x:c r="M10">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="N10" s="0">
+      <x:c r="N10">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="O10" s="0">
+      <x:c r="O10">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="P10" s="0">
+      <x:c r="P10">
         <x:v>-29</x:v>
       </x:c>
     </x:row>
@@ -897,136 +894,136 @@
       <x:c r="A11" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C11" s="0">
+      <x:c r="C11">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="0">
+      <x:c r="D11">
         <x:v>-83</x:v>
       </x:c>
-      <x:c r="E11" s="0">
+      <x:c r="E11">
         <x:v>-105</x:v>
       </x:c>
-      <x:c r="F11" s="0">
+      <x:c r="F11">
         <x:v>-31</x:v>
       </x:c>
-      <x:c r="G11" s="0">
+      <x:c r="G11">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H11" s="0">
+      <x:c r="H11">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="I11" s="0">
+      <x:c r="I11">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J11" s="0">
+      <x:c r="J11">
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="K11" s="0">
+      <x:c r="K11">
         <x:v>-110</x:v>
       </x:c>
-      <x:c r="L11" s="0">
+      <x:c r="L11">
         <x:v>-59</x:v>
       </x:c>
-      <x:c r="M11" s="0">
+      <x:c r="M11">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="N11" s="0">
+      <x:c r="N11">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="O11" s="0">
+      <x:c r="O11">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="P11" s="0">
+      <x:c r="P11">
         <x:v>-32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
       <x:c r="A12" s="1"/>
-      <x:c r="C12" s="0">
+      <x:c r="C12">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D12" s="0">
+      <x:c r="D12">
         <x:v>-91</x:v>
       </x:c>
-      <x:c r="E12" s="0">
+      <x:c r="E12">
         <x:v>-115</x:v>
       </x:c>
-      <x:c r="F12" s="0">
+      <x:c r="F12">
         <x:v>-34</x:v>
       </x:c>
-      <x:c r="G12" s="0">
+      <x:c r="G12">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H12" s="0">
+      <x:c r="H12">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="I12" s="0">
+      <x:c r="I12">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J12" s="0">
+      <x:c r="J12">
         <x:v>-65</x:v>
       </x:c>
-      <x:c r="K12" s="0">
+      <x:c r="K12">
         <x:v>-120</x:v>
       </x:c>
-      <x:c r="L12" s="0">
+      <x:c r="L12">
         <x:v>-64</x:v>
       </x:c>
-      <x:c r="M12" s="0">
+      <x:c r="M12">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="N12" s="0">
+      <x:c r="N12">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="O12" s="0">
+      <x:c r="O12">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="P12" s="0">
+      <x:c r="P12">
         <x:v>-35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
       <x:c r="A13" s="1"/>
-      <x:c r="C13" s="0">
+      <x:c r="C13">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D13" s="0">
+      <x:c r="D13">
         <x:v>-98</x:v>
       </x:c>
-      <x:c r="E13" s="0">
+      <x:c r="E13">
         <x:v>-125</x:v>
       </x:c>
-      <x:c r="F13" s="0">
+      <x:c r="F13">
         <x:v>-36</x:v>
       </x:c>
-      <x:c r="G13" s="0">
+      <x:c r="G13">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H13" s="0">
+      <x:c r="H13">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="I13" s="0">
+      <x:c r="I13">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J13" s="0">
+      <x:c r="J13">
         <x:v>-71</x:v>
       </x:c>
-      <x:c r="K13" s="0">
+      <x:c r="K13">
         <x:v>-130</x:v>
       </x:c>
-      <x:c r="L13" s="0">
+      <x:c r="L13">
         <x:v>-70</x:v>
       </x:c>
-      <x:c r="M13" s="0">
+      <x:c r="M13">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="N13" s="0">
+      <x:c r="N13">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="O13" s="0">
+      <x:c r="O13">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="P13" s="0">
+      <x:c r="P13">
         <x:v>-37</x:v>
       </x:c>
     </x:row>
@@ -1034,136 +1031,136 @@
       <x:c r="A14" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="0">
+      <x:c r="C14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D14" s="0">
+      <x:c r="D14">
         <x:v>-106</x:v>
       </x:c>
-      <x:c r="E14" s="0">
+      <x:c r="E14">
         <x:v>-134</x:v>
       </x:c>
-      <x:c r="F14" s="0">
+      <x:c r="F14">
         <x:v>-39</x:v>
       </x:c>
-      <x:c r="G14" s="0">
+      <x:c r="G14">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H14" s="0">
+      <x:c r="H14">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="I14" s="0">
+      <x:c r="I14">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J14" s="0">
+      <x:c r="J14">
         <x:v>-76</x:v>
       </x:c>
-      <x:c r="K14" s="0">
+      <x:c r="K14">
         <x:v>-140</x:v>
       </x:c>
-      <x:c r="L14" s="0">
+      <x:c r="L14">
         <x:v>-75</x:v>
       </x:c>
-      <x:c r="M14" s="0">
+      <x:c r="M14">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N14" s="0">
+      <x:c r="N14">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="O14" s="0">
+      <x:c r="O14">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="P14" s="0">
+      <x:c r="P14">
         <x:v>-40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
       <x:c r="A15" s="1"/>
-      <x:c r="C15" s="0">
+      <x:c r="C15">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D15" s="0">
+      <x:c r="D15">
         <x:v>-114</x:v>
       </x:c>
-      <x:c r="E15" s="0">
+      <x:c r="E15">
         <x:v>-144</x:v>
       </x:c>
-      <x:c r="F15" s="0">
+      <x:c r="F15">
         <x:v>-42</x:v>
       </x:c>
-      <x:c r="G15" s="0">
+      <x:c r="G15">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H15" s="0">
+      <x:c r="H15">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="I15" s="0">
+      <x:c r="I15">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="J15" s="0">
+      <x:c r="J15">
         <x:v>-82</x:v>
       </x:c>
-      <x:c r="K15" s="0">
+      <x:c r="K15">
         <x:v>-150</x:v>
       </x:c>
-      <x:c r="L15" s="0">
+      <x:c r="L15">
         <x:v>-80</x:v>
       </x:c>
-      <x:c r="M15" s="0">
+      <x:c r="M15">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="N15" s="0">
+      <x:c r="N15">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="O15" s="0">
+      <x:c r="O15">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="P15" s="0">
+      <x:c r="P15">
         <x:v>-43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
       <x:c r="A16" s="1"/>
-      <x:c r="C16" s="0">
+      <x:c r="C16">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D16" s="0">
+      <x:c r="D16">
         <x:v>-121</x:v>
       </x:c>
-      <x:c r="E16" s="0">
+      <x:c r="E16">
         <x:v>-153</x:v>
       </x:c>
-      <x:c r="F16" s="0">
+      <x:c r="F16">
         <x:v>-45</x:v>
       </x:c>
-      <x:c r="G16" s="0">
+      <x:c r="G16">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H16" s="0">
+      <x:c r="H16">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="I16" s="0">
+      <x:c r="I16">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="J16" s="0">
+      <x:c r="J16">
         <x:v>-87</x:v>
       </x:c>
-      <x:c r="K16" s="0">
+      <x:c r="K16">
         <x:v>-160</x:v>
       </x:c>
-      <x:c r="L16" s="0">
+      <x:c r="L16">
         <x:v>-86</x:v>
       </x:c>
-      <x:c r="M16" s="0">
+      <x:c r="M16">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="N16" s="0">
+      <x:c r="N16">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="O16" s="0">
+      <x:c r="O16">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="P16" s="0">
+      <x:c r="P16">
         <x:v>-46</x:v>
       </x:c>
     </x:row>
@@ -1171,136 +1168,136 @@
       <x:c r="A17" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C17" s="0">
+      <x:c r="C17">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D17" s="0">
+      <x:c r="D17">
         <x:v>-129</x:v>
       </x:c>
-      <x:c r="E17" s="0">
+      <x:c r="E17">
         <x:v>-163</x:v>
       </x:c>
-      <x:c r="F17" s="0">
+      <x:c r="F17">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="G17" s="0">
+      <x:c r="G17">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H17" s="0">
+      <x:c r="H17">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="I17" s="0">
+      <x:c r="I17">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="J17" s="0">
+      <x:c r="J17">
         <x:v>-92</x:v>
       </x:c>
-      <x:c r="K17" s="0">
+      <x:c r="K17">
         <x:v>-170</x:v>
       </x:c>
-      <x:c r="L17" s="0">
+      <x:c r="L17">
         <x:v>-91</x:v>
       </x:c>
-      <x:c r="M17" s="0">
+      <x:c r="M17">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="N17" s="0">
+      <x:c r="N17">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="O17" s="0">
+      <x:c r="O17">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="P17" s="0">
+      <x:c r="P17">
         <x:v>-49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
       <x:c r="A18" s="1"/>
-      <x:c r="C18" s="0">
+      <x:c r="C18">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D18" s="0">
+      <x:c r="D18">
         <x:v>-136</x:v>
       </x:c>
-      <x:c r="E18" s="0">
+      <x:c r="E18">
         <x:v>-173</x:v>
       </x:c>
-      <x:c r="F18" s="0">
+      <x:c r="F18">
         <x:v>-50</x:v>
       </x:c>
-      <x:c r="G18" s="0">
+      <x:c r="G18">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H18" s="0">
+      <x:c r="H18">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="I18" s="0">
+      <x:c r="I18">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="J18" s="0">
+      <x:c r="J18">
         <x:v>-98</x:v>
       </x:c>
-      <x:c r="K18" s="0">
+      <x:c r="K18">
         <x:v>-180</x:v>
       </x:c>
-      <x:c r="L18" s="0">
+      <x:c r="L18">
         <x:v>-97</x:v>
       </x:c>
-      <x:c r="M18" s="0">
+      <x:c r="M18">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="N18" s="0">
+      <x:c r="N18">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="O18" s="0">
+      <x:c r="O18">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="P18" s="0">
+      <x:c r="P18">
         <x:v>-52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
       <x:c r="A19" s="1"/>
-      <x:c r="C19" s="0">
+      <x:c r="C19">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D19" s="0">
+      <x:c r="D19">
         <x:v>-144</x:v>
       </x:c>
-      <x:c r="E19" s="0">
+      <x:c r="E19">
         <x:v>-182</x:v>
       </x:c>
-      <x:c r="F19" s="0">
+      <x:c r="F19">
         <x:v>-53</x:v>
       </x:c>
-      <x:c r="G19" s="0">
+      <x:c r="G19">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H19" s="0">
+      <x:c r="H19">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="I19" s="0">
+      <x:c r="I19">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="J19" s="0">
+      <x:c r="J19">
         <x:v>-103</x:v>
       </x:c>
-      <x:c r="K19" s="0">
+      <x:c r="K19">
         <x:v>-190</x:v>
       </x:c>
-      <x:c r="L19" s="0">
+      <x:c r="L19">
         <x:v>-102</x:v>
       </x:c>
-      <x:c r="M19" s="0">
+      <x:c r="M19">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N19" s="0">
+      <x:c r="N19">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="O19" s="0">
+      <x:c r="O19">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="P19" s="0">
+      <x:c r="P19">
         <x:v>-55</x:v>
       </x:c>
     </x:row>
@@ -1313,15 +1310,11 @@
     <x:mergeCell ref="A14:A16"/>
     <x:mergeCell ref="A17:A19"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="line" dateAxis="0" displayEmptyCellsAs="span" markers="1" high="1" low="1" first="1" last="1" negative="1" displayXAxis="0" displayHidden="0" minAxisType="group" maxAxisType="group" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" displayEmptyCellsAs="span" markers="1" high="1" low="1" first="1" last="1" negative="1" minAxisType="group" maxAxisType="group" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5F5F5F"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -1345,7 +1338,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="line" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="1" low="1" first="1" last="1" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" displayEmptyCellsAs="span" high="1" low="1" first="1" last="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5687C2"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -1369,7 +1362,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" manualMax="100" manualMin="-80" lineWeight="0.75" type="line" dateAxis="0" displayEmptyCellsAs="span" markers="1" high="0" low="0" first="0" last="0" negative="1" displayXAxis="0" displayHidden="0" minAxisType="custom" maxAxisType="custom" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" manualMax="100" manualMin="-80" displayEmptyCellsAs="span" markers="1" negative="1" minAxisType="custom" maxAxisType="custom" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FFC6EFCE"/>
           <x14:colorNegative rgb="FFFFC7CE"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -1393,7 +1386,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="line" dateAxis="1" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="0" last="0" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" dateAxis="1" displayEmptyCellsAs="span" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5F5F5F"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -1418,7 +1411,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="2" type="line" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="0" last="0" negative="0" displayXAxis="1" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="2" displayEmptyCellsAs="span" displayXAxis="1" rightToLeft="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF00B050"/>
           <x14:colorNegative rgb="FFFF0000"/>
           <x14:colorAxis rgb="FFFF0000"/>
@@ -1442,7 +1435,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="line" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="1" last="1" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" displayEmptyCellsAs="span" first="1" last="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FFC6EFCE"/>
           <x14:colorNegative rgb="FFFFC7CE"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -1474,14 +1467,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="30.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -1532,136 +1522,136 @@
       <x:c r="A2" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>-15</x:v>
       </x:c>
-      <x:c r="E2" s="0">
+      <x:c r="E2">
         <x:v>-19</x:v>
       </x:c>
-      <x:c r="F2" s="0">
+      <x:c r="F2">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="G2" s="0">
+      <x:c r="G2">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H2" s="0">
+      <x:c r="H2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="0">
+      <x:c r="I2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J2" s="0">
+      <x:c r="J2">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="K2" s="0">
+      <x:c r="K2">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="L2" s="0">
+      <x:c r="L2">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="M2" s="0">
+      <x:c r="M2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="N2" s="0">
+      <x:c r="N2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O2" s="0">
+      <x:c r="O2">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="P2" s="0">
+      <x:c r="P2">
         <x:v>-6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
       <x:c r="A3" s="1"/>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>-23</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>-29</x:v>
       </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="F3">
         <x:v>-8</x:v>
       </x:c>
-      <x:c r="G3" s="0">
+      <x:c r="G3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H3" s="0">
+      <x:c r="H3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I3" s="0">
+      <x:c r="I3">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J3" s="0">
+      <x:c r="J3">
         <x:v>-16</x:v>
       </x:c>
-      <x:c r="K3" s="0">
+      <x:c r="K3">
         <x:v>-30</x:v>
       </x:c>
-      <x:c r="L3" s="0">
+      <x:c r="L3">
         <x:v>-16</x:v>
       </x:c>
-      <x:c r="M3" s="0">
+      <x:c r="M3">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="N3" s="0">
+      <x:c r="N3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O3" s="0">
+      <x:c r="O3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P3" s="0">
+      <x:c r="P3">
         <x:v>-9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
       <x:c r="A4" s="1"/>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>-30</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="G4" s="0">
+      <x:c r="G4">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H4" s="0">
+      <x:c r="H4">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I4" s="0">
+      <x:c r="I4">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J4" s="0">
+      <x:c r="J4">
         <x:v>-22</x:v>
       </x:c>
-      <x:c r="K4" s="0">
+      <x:c r="K4">
         <x:v>-40</x:v>
       </x:c>
-      <x:c r="L4" s="0">
+      <x:c r="L4">
         <x:v>-21</x:v>
       </x:c>
-      <x:c r="M4" s="0">
+      <x:c r="M4">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="N4" s="0">
+      <x:c r="N4">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="O4" s="0">
+      <x:c r="O4">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P4" s="0">
+      <x:c r="P4">
         <x:v>-12</x:v>
       </x:c>
     </x:row>
@@ -1669,136 +1659,136 @@
       <x:c r="A5" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>-14</x:v>
       </x:c>
-      <x:c r="G5" s="0">
+      <x:c r="G5">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H5" s="0">
+      <x:c r="H5">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="I5" s="0">
+      <x:c r="I5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J5" s="0">
+      <x:c r="J5">
         <x:v>-27</x:v>
       </x:c>
-      <x:c r="K5" s="0">
+      <x:c r="K5">
         <x:v>-50</x:v>
       </x:c>
-      <x:c r="L5" s="0">
+      <x:c r="L5">
         <x:v>-27</x:v>
       </x:c>
-      <x:c r="M5" s="0">
+      <x:c r="M5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="N5" s="0">
+      <x:c r="N5">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="O5" s="0">
+      <x:c r="O5">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="P5" s="0">
+      <x:c r="P5">
         <x:v>-14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
       <x:c r="A6" s="1"/>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>-45</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>-58</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F6">
         <x:v>-17</x:v>
       </x:c>
-      <x:c r="G6" s="0">
+      <x:c r="G6">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H6" s="0">
+      <x:c r="H6">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I6" s="0">
+      <x:c r="I6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J6" s="0">
+      <x:c r="J6">
         <x:v>-33</x:v>
       </x:c>
-      <x:c r="K6" s="0">
+      <x:c r="K6">
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="L6" s="0">
+      <x:c r="L6">
         <x:v>-32</x:v>
       </x:c>
-      <x:c r="M6" s="0">
+      <x:c r="M6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="N6" s="0">
+      <x:c r="N6">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="O6" s="0">
+      <x:c r="O6">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="P6" s="0">
+      <x:c r="P6">
         <x:v>-17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
       <x:c r="A7" s="1"/>
-      <x:c r="C7" s="0">
+      <x:c r="C7">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="0">
+      <x:c r="D7">
         <x:v>-53</x:v>
       </x:c>
-      <x:c r="E7" s="0">
+      <x:c r="E7">
         <x:v>-67</x:v>
       </x:c>
-      <x:c r="F7" s="0">
+      <x:c r="F7">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="G7" s="0">
+      <x:c r="G7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H7" s="0">
+      <x:c r="H7">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="I7" s="0">
+      <x:c r="I7">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J7" s="0">
+      <x:c r="J7">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="K7" s="0">
+      <x:c r="K7">
         <x:v>-70</x:v>
       </x:c>
-      <x:c r="L7" s="0">
+      <x:c r="L7">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="M7" s="0">
+      <x:c r="M7">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="N7" s="0">
+      <x:c r="N7">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="O7" s="0">
+      <x:c r="O7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="P7" s="0">
+      <x:c r="P7">
         <x:v>-20</x:v>
       </x:c>
     </x:row>
@@ -1806,136 +1796,136 @@
       <x:c r="A8" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C8" s="0">
+      <x:c r="C8">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D8" s="0">
+      <x:c r="D8">
         <x:v>-61</x:v>
       </x:c>
-      <x:c r="E8" s="0">
+      <x:c r="E8">
         <x:v>-77</x:v>
       </x:c>
-      <x:c r="F8" s="0">
+      <x:c r="F8">
         <x:v>-22</x:v>
       </x:c>
-      <x:c r="G8" s="0">
+      <x:c r="G8">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H8" s="0">
+      <x:c r="H8">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="I8" s="0">
+      <x:c r="I8">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="J8" s="0">
+      <x:c r="J8">
         <x:v>-44</x:v>
       </x:c>
-      <x:c r="K8" s="0">
+      <x:c r="K8">
         <x:v>-80</x:v>
       </x:c>
-      <x:c r="L8" s="0">
+      <x:c r="L8">
         <x:v>-43</x:v>
       </x:c>
-      <x:c r="M8" s="0">
+      <x:c r="M8">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="N8" s="0">
+      <x:c r="N8">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="O8" s="0">
+      <x:c r="O8">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="P8" s="0">
+      <x:c r="P8">
         <x:v>-23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
       <x:c r="A9" s="1"/>
-      <x:c r="C9" s="0">
+      <x:c r="C9">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D9" s="0">
+      <x:c r="D9">
         <x:v>-68</x:v>
       </x:c>
-      <x:c r="E9" s="0">
+      <x:c r="E9">
         <x:v>-86</x:v>
       </x:c>
-      <x:c r="F9" s="0">
+      <x:c r="F9">
         <x:v>-25</x:v>
       </x:c>
-      <x:c r="G9" s="0">
+      <x:c r="G9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H9" s="0">
+      <x:c r="H9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="I9" s="0">
+      <x:c r="I9">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J9" s="0">
+      <x:c r="J9">
         <x:v>-49</x:v>
       </x:c>
-      <x:c r="K9" s="0">
+      <x:c r="K9">
         <x:v>-90</x:v>
       </x:c>
-      <x:c r="L9" s="0">
+      <x:c r="L9">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="M9" s="0">
+      <x:c r="M9">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="N9" s="0">
+      <x:c r="N9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="O9" s="0">
+      <x:c r="O9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="P9" s="0">
+      <x:c r="P9">
         <x:v>-26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
       <x:c r="A10" s="1"/>
-      <x:c r="C10" s="0">
+      <x:c r="C10">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="0">
+      <x:c r="D10">
         <x:v>-76</x:v>
       </x:c>
-      <x:c r="E10" s="0">
+      <x:c r="E10">
         <x:v>-96</x:v>
       </x:c>
-      <x:c r="F10" s="0">
+      <x:c r="F10">
         <x:v>-28</x:v>
       </x:c>
-      <x:c r="G10" s="0">
+      <x:c r="G10">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H10" s="0">
+      <x:c r="H10">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="I10" s="0">
+      <x:c r="I10">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J10" s="0">
+      <x:c r="J10">
         <x:v>-54</x:v>
       </x:c>
-      <x:c r="K10" s="0">
+      <x:c r="K10">
         <x:v>-100</x:v>
       </x:c>
-      <x:c r="L10" s="0">
+      <x:c r="L10">
         <x:v>-54</x:v>
       </x:c>
-      <x:c r="M10" s="0">
+      <x:c r="M10">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="N10" s="0">
+      <x:c r="N10">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="O10" s="0">
+      <x:c r="O10">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="P10" s="0">
+      <x:c r="P10">
         <x:v>-29</x:v>
       </x:c>
     </x:row>
@@ -1943,136 +1933,136 @@
       <x:c r="A11" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C11" s="0">
+      <x:c r="C11">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="0">
+      <x:c r="D11">
         <x:v>-83</x:v>
       </x:c>
-      <x:c r="E11" s="0">
+      <x:c r="E11">
         <x:v>-105</x:v>
       </x:c>
-      <x:c r="F11" s="0">
+      <x:c r="F11">
         <x:v>-31</x:v>
       </x:c>
-      <x:c r="G11" s="0">
+      <x:c r="G11">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H11" s="0">
+      <x:c r="H11">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="I11" s="0">
+      <x:c r="I11">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J11" s="0">
+      <x:c r="J11">
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="K11" s="0">
+      <x:c r="K11">
         <x:v>-110</x:v>
       </x:c>
-      <x:c r="L11" s="0">
+      <x:c r="L11">
         <x:v>-59</x:v>
       </x:c>
-      <x:c r="M11" s="0">
+      <x:c r="M11">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="N11" s="0">
+      <x:c r="N11">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="O11" s="0">
+      <x:c r="O11">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="P11" s="0">
+      <x:c r="P11">
         <x:v>-32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
       <x:c r="A12" s="1"/>
-      <x:c r="C12" s="0">
+      <x:c r="C12">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D12" s="0">
+      <x:c r="D12">
         <x:v>-91</x:v>
       </x:c>
-      <x:c r="E12" s="0">
+      <x:c r="E12">
         <x:v>-115</x:v>
       </x:c>
-      <x:c r="F12" s="0">
+      <x:c r="F12">
         <x:v>-34</x:v>
       </x:c>
-      <x:c r="G12" s="0">
+      <x:c r="G12">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H12" s="0">
+      <x:c r="H12">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="I12" s="0">
+      <x:c r="I12">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J12" s="0">
+      <x:c r="J12">
         <x:v>-65</x:v>
       </x:c>
-      <x:c r="K12" s="0">
+      <x:c r="K12">
         <x:v>-120</x:v>
       </x:c>
-      <x:c r="L12" s="0">
+      <x:c r="L12">
         <x:v>-64</x:v>
       </x:c>
-      <x:c r="M12" s="0">
+      <x:c r="M12">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="N12" s="0">
+      <x:c r="N12">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="O12" s="0">
+      <x:c r="O12">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="P12" s="0">
+      <x:c r="P12">
         <x:v>-35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
       <x:c r="A13" s="1"/>
-      <x:c r="C13" s="0">
+      <x:c r="C13">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D13" s="0">
+      <x:c r="D13">
         <x:v>-98</x:v>
       </x:c>
-      <x:c r="E13" s="0">
+      <x:c r="E13">
         <x:v>-125</x:v>
       </x:c>
-      <x:c r="F13" s="0">
+      <x:c r="F13">
         <x:v>-36</x:v>
       </x:c>
-      <x:c r="G13" s="0">
+      <x:c r="G13">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H13" s="0">
+      <x:c r="H13">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="I13" s="0">
+      <x:c r="I13">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J13" s="0">
+      <x:c r="J13">
         <x:v>-71</x:v>
       </x:c>
-      <x:c r="K13" s="0">
+      <x:c r="K13">
         <x:v>-130</x:v>
       </x:c>
-      <x:c r="L13" s="0">
+      <x:c r="L13">
         <x:v>-70</x:v>
       </x:c>
-      <x:c r="M13" s="0">
+      <x:c r="M13">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="N13" s="0">
+      <x:c r="N13">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="O13" s="0">
+      <x:c r="O13">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="P13" s="0">
+      <x:c r="P13">
         <x:v>-37</x:v>
       </x:c>
     </x:row>
@@ -2080,136 +2070,136 @@
       <x:c r="A14" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C14" s="0">
+      <x:c r="C14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D14" s="0">
+      <x:c r="D14">
         <x:v>-106</x:v>
       </x:c>
-      <x:c r="E14" s="0">
+      <x:c r="E14">
         <x:v>-134</x:v>
       </x:c>
-      <x:c r="F14" s="0">
+      <x:c r="F14">
         <x:v>-39</x:v>
       </x:c>
-      <x:c r="G14" s="0">
+      <x:c r="G14">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H14" s="0">
+      <x:c r="H14">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="I14" s="0">
+      <x:c r="I14">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J14" s="0">
+      <x:c r="J14">
         <x:v>-76</x:v>
       </x:c>
-      <x:c r="K14" s="0">
+      <x:c r="K14">
         <x:v>-140</x:v>
       </x:c>
-      <x:c r="L14" s="0">
+      <x:c r="L14">
         <x:v>-75</x:v>
       </x:c>
-      <x:c r="M14" s="0">
+      <x:c r="M14">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N14" s="0">
+      <x:c r="N14">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="O14" s="0">
+      <x:c r="O14">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="P14" s="0">
+      <x:c r="P14">
         <x:v>-40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
       <x:c r="A15" s="1"/>
-      <x:c r="C15" s="0">
+      <x:c r="C15">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D15" s="0">
+      <x:c r="D15">
         <x:v>-114</x:v>
       </x:c>
-      <x:c r="E15" s="0">
+      <x:c r="E15">
         <x:v>-144</x:v>
       </x:c>
-      <x:c r="F15" s="0">
+      <x:c r="F15">
         <x:v>-42</x:v>
       </x:c>
-      <x:c r="G15" s="0">
+      <x:c r="G15">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H15" s="0">
+      <x:c r="H15">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="I15" s="0">
+      <x:c r="I15">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="J15" s="0">
+      <x:c r="J15">
         <x:v>-82</x:v>
       </x:c>
-      <x:c r="K15" s="0">
+      <x:c r="K15">
         <x:v>-150</x:v>
       </x:c>
-      <x:c r="L15" s="0">
+      <x:c r="L15">
         <x:v>-80</x:v>
       </x:c>
-      <x:c r="M15" s="0">
+      <x:c r="M15">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="N15" s="0">
+      <x:c r="N15">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="O15" s="0">
+      <x:c r="O15">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="P15" s="0">
+      <x:c r="P15">
         <x:v>-43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
       <x:c r="A16" s="1"/>
-      <x:c r="C16" s="0">
+      <x:c r="C16">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D16" s="0">
+      <x:c r="D16">
         <x:v>-121</x:v>
       </x:c>
-      <x:c r="E16" s="0">
+      <x:c r="E16">
         <x:v>-153</x:v>
       </x:c>
-      <x:c r="F16" s="0">
+      <x:c r="F16">
         <x:v>-45</x:v>
       </x:c>
-      <x:c r="G16" s="0">
+      <x:c r="G16">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H16" s="0">
+      <x:c r="H16">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="I16" s="0">
+      <x:c r="I16">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="J16" s="0">
+      <x:c r="J16">
         <x:v>-87</x:v>
       </x:c>
-      <x:c r="K16" s="0">
+      <x:c r="K16">
         <x:v>-160</x:v>
       </x:c>
-      <x:c r="L16" s="0">
+      <x:c r="L16">
         <x:v>-86</x:v>
       </x:c>
-      <x:c r="M16" s="0">
+      <x:c r="M16">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="N16" s="0">
+      <x:c r="N16">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="O16" s="0">
+      <x:c r="O16">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="P16" s="0">
+      <x:c r="P16">
         <x:v>-46</x:v>
       </x:c>
     </x:row>
@@ -2217,136 +2207,136 @@
       <x:c r="A17" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C17" s="0">
+      <x:c r="C17">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D17" s="0">
+      <x:c r="D17">
         <x:v>-129</x:v>
       </x:c>
-      <x:c r="E17" s="0">
+      <x:c r="E17">
         <x:v>-163</x:v>
       </x:c>
-      <x:c r="F17" s="0">
+      <x:c r="F17">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="G17" s="0">
+      <x:c r="G17">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H17" s="0">
+      <x:c r="H17">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="I17" s="0">
+      <x:c r="I17">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="J17" s="0">
+      <x:c r="J17">
         <x:v>-92</x:v>
       </x:c>
-      <x:c r="K17" s="0">
+      <x:c r="K17">
         <x:v>-170</x:v>
       </x:c>
-      <x:c r="L17" s="0">
+      <x:c r="L17">
         <x:v>-91</x:v>
       </x:c>
-      <x:c r="M17" s="0">
+      <x:c r="M17">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="N17" s="0">
+      <x:c r="N17">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="O17" s="0">
+      <x:c r="O17">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="P17" s="0">
+      <x:c r="P17">
         <x:v>-49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
       <x:c r="A18" s="1"/>
-      <x:c r="C18" s="0">
+      <x:c r="C18">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D18" s="0">
+      <x:c r="D18">
         <x:v>-136</x:v>
       </x:c>
-      <x:c r="E18" s="0">
+      <x:c r="E18">
         <x:v>-173</x:v>
       </x:c>
-      <x:c r="F18" s="0">
+      <x:c r="F18">
         <x:v>-50</x:v>
       </x:c>
-      <x:c r="G18" s="0">
+      <x:c r="G18">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H18" s="0">
+      <x:c r="H18">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="I18" s="0">
+      <x:c r="I18">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="J18" s="0">
+      <x:c r="J18">
         <x:v>-98</x:v>
       </x:c>
-      <x:c r="K18" s="0">
+      <x:c r="K18">
         <x:v>-180</x:v>
       </x:c>
-      <x:c r="L18" s="0">
+      <x:c r="L18">
         <x:v>-97</x:v>
       </x:c>
-      <x:c r="M18" s="0">
+      <x:c r="M18">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="N18" s="0">
+      <x:c r="N18">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="O18" s="0">
+      <x:c r="O18">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="P18" s="0">
+      <x:c r="P18">
         <x:v>-52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
       <x:c r="A19" s="1"/>
-      <x:c r="C19" s="0">
+      <x:c r="C19">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D19" s="0">
+      <x:c r="D19">
         <x:v>-144</x:v>
       </x:c>
-      <x:c r="E19" s="0">
+      <x:c r="E19">
         <x:v>-182</x:v>
       </x:c>
-      <x:c r="F19" s="0">
+      <x:c r="F19">
         <x:v>-53</x:v>
       </x:c>
-      <x:c r="G19" s="0">
+      <x:c r="G19">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H19" s="0">
+      <x:c r="H19">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="I19" s="0">
+      <x:c r="I19">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="J19" s="0">
+      <x:c r="J19">
         <x:v>-103</x:v>
       </x:c>
-      <x:c r="K19" s="0">
+      <x:c r="K19">
         <x:v>-190</x:v>
       </x:c>
-      <x:c r="L19" s="0">
+      <x:c r="L19">
         <x:v>-102</x:v>
       </x:c>
-      <x:c r="M19" s="0">
+      <x:c r="M19">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N19" s="0">
+      <x:c r="N19">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="O19" s="0">
+      <x:c r="O19">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="P19" s="0">
+      <x:c r="P19">
         <x:v>-55</x:v>
       </x:c>
     </x:row>
@@ -2359,22 +2349,11 @@
     <x:mergeCell ref="A14:A16"/>
     <x:mergeCell ref="A17:A19"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="column" dateAxis="0" displayEmptyCellsAs="span" markers="1" high="1" low="1" first="1" last="1" negative="1" displayXAxis="0" displayHidden="0" minAxisType="group" maxAxisType="group" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="column" displayEmptyCellsAs="span" markers="1" high="1" low="1" first="1" last="1" negative="1" minAxisType="group" maxAxisType="group" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5F5F5F"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -2398,7 +2377,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="column" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="1" low="1" first="1" last="1" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="column" displayEmptyCellsAs="span" high="1" low="1" first="1" last="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5687C2"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -2422,7 +2401,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" manualMax="100" manualMin="-80" lineWeight="0.75" type="column" dateAxis="0" displayEmptyCellsAs="span" markers="1" high="0" low="0" first="0" last="0" negative="1" displayXAxis="0" displayHidden="0" minAxisType="custom" maxAxisType="custom" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" manualMax="100" manualMin="-80" type="column" displayEmptyCellsAs="span" markers="1" negative="1" minAxisType="custom" maxAxisType="custom" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FFC6EFCE"/>
           <x14:colorNegative rgb="FFFFC7CE"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -2446,7 +2425,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="column" dateAxis="1" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="0" last="0" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="column" dateAxis="1" displayEmptyCellsAs="span" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5F5F5F"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -2471,7 +2450,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="2" type="column" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="0" last="0" negative="0" displayXAxis="1" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="2" type="column" displayEmptyCellsAs="span" displayXAxis="1" rightToLeft="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF00B050"/>
           <x14:colorNegative rgb="FFFF0000"/>
           <x14:colorAxis rgb="FFFF0000"/>
@@ -2495,7 +2474,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="column" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="1" last="1" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="column" displayEmptyCellsAs="span" first="1" last="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FFC6EFCE"/>
           <x14:colorNegative rgb="FFFFC7CE"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -2527,14 +2506,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="30.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -2585,136 +2561,136 @@
       <x:c r="A2" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>-15</x:v>
       </x:c>
-      <x:c r="E2" s="0">
+      <x:c r="E2">
         <x:v>-19</x:v>
       </x:c>
-      <x:c r="F2" s="0">
+      <x:c r="F2">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="G2" s="0">
+      <x:c r="G2">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H2" s="0">
+      <x:c r="H2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="0">
+      <x:c r="I2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J2" s="0">
+      <x:c r="J2">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="K2" s="0">
+      <x:c r="K2">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="L2" s="0">
+      <x:c r="L2">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="M2" s="0">
+      <x:c r="M2">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="N2" s="0">
+      <x:c r="N2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O2" s="0">
+      <x:c r="O2">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="P2" s="0">
+      <x:c r="P2">
         <x:v>-6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
       <x:c r="A3" s="1"/>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>-23</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>-29</x:v>
       </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="F3">
         <x:v>-8</x:v>
       </x:c>
-      <x:c r="G3" s="0">
+      <x:c r="G3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H3" s="0">
+      <x:c r="H3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I3" s="0">
+      <x:c r="I3">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J3" s="0">
+      <x:c r="J3">
         <x:v>-16</x:v>
       </x:c>
-      <x:c r="K3" s="0">
+      <x:c r="K3">
         <x:v>-30</x:v>
       </x:c>
-      <x:c r="L3" s="0">
+      <x:c r="L3">
         <x:v>-16</x:v>
       </x:c>
-      <x:c r="M3" s="0">
+      <x:c r="M3">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="N3" s="0">
+      <x:c r="N3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O3" s="0">
+      <x:c r="O3">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="P3" s="0">
+      <x:c r="P3">
         <x:v>-9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
       <x:c r="A4" s="1"/>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>-30</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>-11</x:v>
       </x:c>
-      <x:c r="G4" s="0">
+      <x:c r="G4">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H4" s="0">
+      <x:c r="H4">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I4" s="0">
+      <x:c r="I4">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J4" s="0">
+      <x:c r="J4">
         <x:v>-22</x:v>
       </x:c>
-      <x:c r="K4" s="0">
+      <x:c r="K4">
         <x:v>-40</x:v>
       </x:c>
-      <x:c r="L4" s="0">
+      <x:c r="L4">
         <x:v>-21</x:v>
       </x:c>
-      <x:c r="M4" s="0">
+      <x:c r="M4">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="N4" s="0">
+      <x:c r="N4">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="O4" s="0">
+      <x:c r="O4">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P4" s="0">
+      <x:c r="P4">
         <x:v>-12</x:v>
       </x:c>
     </x:row>
@@ -2722,136 +2698,136 @@
       <x:c r="A5" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>-14</x:v>
       </x:c>
-      <x:c r="G5" s="0">
+      <x:c r="G5">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H5" s="0">
+      <x:c r="H5">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="I5" s="0">
+      <x:c r="I5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J5" s="0">
+      <x:c r="J5">
         <x:v>-27</x:v>
       </x:c>
-      <x:c r="K5" s="0">
+      <x:c r="K5">
         <x:v>-50</x:v>
       </x:c>
-      <x:c r="L5" s="0">
+      <x:c r="L5">
         <x:v>-27</x:v>
       </x:c>
-      <x:c r="M5" s="0">
+      <x:c r="M5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="N5" s="0">
+      <x:c r="N5">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="O5" s="0">
+      <x:c r="O5">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="P5" s="0">
+      <x:c r="P5">
         <x:v>-14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
       <x:c r="A6" s="1"/>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>-45</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>-58</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F6">
         <x:v>-17</x:v>
       </x:c>
-      <x:c r="G6" s="0">
+      <x:c r="G6">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H6" s="0">
+      <x:c r="H6">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I6" s="0">
+      <x:c r="I6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J6" s="0">
+      <x:c r="J6">
         <x:v>-33</x:v>
       </x:c>
-      <x:c r="K6" s="0">
+      <x:c r="K6">
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="L6" s="0">
+      <x:c r="L6">
         <x:v>-32</x:v>
       </x:c>
-      <x:c r="M6" s="0">
+      <x:c r="M6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="N6" s="0">
+      <x:c r="N6">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="O6" s="0">
+      <x:c r="O6">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="P6" s="0">
+      <x:c r="P6">
         <x:v>-17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
       <x:c r="A7" s="1"/>
-      <x:c r="C7" s="0">
+      <x:c r="C7">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="0">
+      <x:c r="D7">
         <x:v>-53</x:v>
       </x:c>
-      <x:c r="E7" s="0">
+      <x:c r="E7">
         <x:v>-67</x:v>
       </x:c>
-      <x:c r="F7" s="0">
+      <x:c r="F7">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="G7" s="0">
+      <x:c r="G7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H7" s="0">
+      <x:c r="H7">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="I7" s="0">
+      <x:c r="I7">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J7" s="0">
+      <x:c r="J7">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="K7" s="0">
+      <x:c r="K7">
         <x:v>-70</x:v>
       </x:c>
-      <x:c r="L7" s="0">
+      <x:c r="L7">
         <x:v>-38</x:v>
       </x:c>
-      <x:c r="M7" s="0">
+      <x:c r="M7">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="N7" s="0">
+      <x:c r="N7">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="O7" s="0">
+      <x:c r="O7">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="P7" s="0">
+      <x:c r="P7">
         <x:v>-20</x:v>
       </x:c>
     </x:row>
@@ -2859,136 +2835,136 @@
       <x:c r="A8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="0">
+      <x:c r="C8">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D8" s="0">
+      <x:c r="D8">
         <x:v>-61</x:v>
       </x:c>
-      <x:c r="E8" s="0">
+      <x:c r="E8">
         <x:v>-77</x:v>
       </x:c>
-      <x:c r="F8" s="0">
+      <x:c r="F8">
         <x:v>-22</x:v>
       </x:c>
-      <x:c r="G8" s="0">
+      <x:c r="G8">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H8" s="0">
+      <x:c r="H8">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="I8" s="0">
+      <x:c r="I8">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="J8" s="0">
+      <x:c r="J8">
         <x:v>-44</x:v>
       </x:c>
-      <x:c r="K8" s="0">
+      <x:c r="K8">
         <x:v>-80</x:v>
       </x:c>
-      <x:c r="L8" s="0">
+      <x:c r="L8">
         <x:v>-43</x:v>
       </x:c>
-      <x:c r="M8" s="0">
+      <x:c r="M8">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="N8" s="0">
+      <x:c r="N8">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="O8" s="0">
+      <x:c r="O8">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="P8" s="0">
+      <x:c r="P8">
         <x:v>-23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
       <x:c r="A9" s="1"/>
-      <x:c r="C9" s="0">
+      <x:c r="C9">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D9" s="0">
+      <x:c r="D9">
         <x:v>-68</x:v>
       </x:c>
-      <x:c r="E9" s="0">
+      <x:c r="E9">
         <x:v>-86</x:v>
       </x:c>
-      <x:c r="F9" s="0">
+      <x:c r="F9">
         <x:v>-25</x:v>
       </x:c>
-      <x:c r="G9" s="0">
+      <x:c r="G9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H9" s="0">
+      <x:c r="H9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="I9" s="0">
+      <x:c r="I9">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J9" s="0">
+      <x:c r="J9">
         <x:v>-49</x:v>
       </x:c>
-      <x:c r="K9" s="0">
+      <x:c r="K9">
         <x:v>-90</x:v>
       </x:c>
-      <x:c r="L9" s="0">
+      <x:c r="L9">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="M9" s="0">
+      <x:c r="M9">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="N9" s="0">
+      <x:c r="N9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="O9" s="0">
+      <x:c r="O9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="P9" s="0">
+      <x:c r="P9">
         <x:v>-26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
       <x:c r="A10" s="1"/>
-      <x:c r="C10" s="0">
+      <x:c r="C10">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="0">
+      <x:c r="D10">
         <x:v>-76</x:v>
       </x:c>
-      <x:c r="E10" s="0">
+      <x:c r="E10">
         <x:v>-96</x:v>
       </x:c>
-      <x:c r="F10" s="0">
+      <x:c r="F10">
         <x:v>-28</x:v>
       </x:c>
-      <x:c r="G10" s="0">
+      <x:c r="G10">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H10" s="0">
+      <x:c r="H10">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="I10" s="0">
+      <x:c r="I10">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="J10" s="0">
+      <x:c r="J10">
         <x:v>-54</x:v>
       </x:c>
-      <x:c r="K10" s="0">
+      <x:c r="K10">
         <x:v>-100</x:v>
       </x:c>
-      <x:c r="L10" s="0">
+      <x:c r="L10">
         <x:v>-54</x:v>
       </x:c>
-      <x:c r="M10" s="0">
+      <x:c r="M10">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="N10" s="0">
+      <x:c r="N10">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="O10" s="0">
+      <x:c r="O10">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="P10" s="0">
+      <x:c r="P10">
         <x:v>-29</x:v>
       </x:c>
     </x:row>
@@ -2996,136 +2972,136 @@
       <x:c r="A11" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="0">
+      <x:c r="C11">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="0">
+      <x:c r="D11">
         <x:v>-83</x:v>
       </x:c>
-      <x:c r="E11" s="0">
+      <x:c r="E11">
         <x:v>-105</x:v>
       </x:c>
-      <x:c r="F11" s="0">
+      <x:c r="F11">
         <x:v>-31</x:v>
       </x:c>
-      <x:c r="G11" s="0">
+      <x:c r="G11">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H11" s="0">
+      <x:c r="H11">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="I11" s="0">
+      <x:c r="I11">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="J11" s="0">
+      <x:c r="J11">
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="K11" s="0">
+      <x:c r="K11">
         <x:v>-110</x:v>
       </x:c>
-      <x:c r="L11" s="0">
+      <x:c r="L11">
         <x:v>-59</x:v>
       </x:c>
-      <x:c r="M11" s="0">
+      <x:c r="M11">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="N11" s="0">
+      <x:c r="N11">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="O11" s="0">
+      <x:c r="O11">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="P11" s="0">
+      <x:c r="P11">
         <x:v>-32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
       <x:c r="A12" s="1"/>
-      <x:c r="C12" s="0">
+      <x:c r="C12">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D12" s="0">
+      <x:c r="D12">
         <x:v>-91</x:v>
       </x:c>
-      <x:c r="E12" s="0">
+      <x:c r="E12">
         <x:v>-115</x:v>
       </x:c>
-      <x:c r="F12" s="0">
+      <x:c r="F12">
         <x:v>-34</x:v>
       </x:c>
-      <x:c r="G12" s="0">
+      <x:c r="G12">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H12" s="0">
+      <x:c r="H12">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="I12" s="0">
+      <x:c r="I12">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J12" s="0">
+      <x:c r="J12">
         <x:v>-65</x:v>
       </x:c>
-      <x:c r="K12" s="0">
+      <x:c r="K12">
         <x:v>-120</x:v>
       </x:c>
-      <x:c r="L12" s="0">
+      <x:c r="L12">
         <x:v>-64</x:v>
       </x:c>
-      <x:c r="M12" s="0">
+      <x:c r="M12">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="N12" s="0">
+      <x:c r="N12">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="O12" s="0">
+      <x:c r="O12">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="P12" s="0">
+      <x:c r="P12">
         <x:v>-35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
       <x:c r="A13" s="1"/>
-      <x:c r="C13" s="0">
+      <x:c r="C13">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D13" s="0">
+      <x:c r="D13">
         <x:v>-98</x:v>
       </x:c>
-      <x:c r="E13" s="0">
+      <x:c r="E13">
         <x:v>-125</x:v>
       </x:c>
-      <x:c r="F13" s="0">
+      <x:c r="F13">
         <x:v>-36</x:v>
       </x:c>
-      <x:c r="G13" s="0">
+      <x:c r="G13">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H13" s="0">
+      <x:c r="H13">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="I13" s="0">
+      <x:c r="I13">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J13" s="0">
+      <x:c r="J13">
         <x:v>-71</x:v>
       </x:c>
-      <x:c r="K13" s="0">
+      <x:c r="K13">
         <x:v>-130</x:v>
       </x:c>
-      <x:c r="L13" s="0">
+      <x:c r="L13">
         <x:v>-70</x:v>
       </x:c>
-      <x:c r="M13" s="0">
+      <x:c r="M13">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="N13" s="0">
+      <x:c r="N13">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="O13" s="0">
+      <x:c r="O13">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="P13" s="0">
+      <x:c r="P13">
         <x:v>-37</x:v>
       </x:c>
     </x:row>
@@ -3133,136 +3109,136 @@
       <x:c r="A14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C14" s="0">
+      <x:c r="C14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D14" s="0">
+      <x:c r="D14">
         <x:v>-106</x:v>
       </x:c>
-      <x:c r="E14" s="0">
+      <x:c r="E14">
         <x:v>-134</x:v>
       </x:c>
-      <x:c r="F14" s="0">
+      <x:c r="F14">
         <x:v>-39</x:v>
       </x:c>
-      <x:c r="G14" s="0">
+      <x:c r="G14">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H14" s="0">
+      <x:c r="H14">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="I14" s="0">
+      <x:c r="I14">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J14" s="0">
+      <x:c r="J14">
         <x:v>-76</x:v>
       </x:c>
-      <x:c r="K14" s="0">
+      <x:c r="K14">
         <x:v>-140</x:v>
       </x:c>
-      <x:c r="L14" s="0">
+      <x:c r="L14">
         <x:v>-75</x:v>
       </x:c>
-      <x:c r="M14" s="0">
+      <x:c r="M14">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N14" s="0">
+      <x:c r="N14">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="O14" s="0">
+      <x:c r="O14">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="P14" s="0">
+      <x:c r="P14">
         <x:v>-40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
       <x:c r="A15" s="1"/>
-      <x:c r="C15" s="0">
+      <x:c r="C15">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D15" s="0">
+      <x:c r="D15">
         <x:v>-114</x:v>
       </x:c>
-      <x:c r="E15" s="0">
+      <x:c r="E15">
         <x:v>-144</x:v>
       </x:c>
-      <x:c r="F15" s="0">
+      <x:c r="F15">
         <x:v>-42</x:v>
       </x:c>
-      <x:c r="G15" s="0">
+      <x:c r="G15">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H15" s="0">
+      <x:c r="H15">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="I15" s="0">
+      <x:c r="I15">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="J15" s="0">
+      <x:c r="J15">
         <x:v>-82</x:v>
       </x:c>
-      <x:c r="K15" s="0">
+      <x:c r="K15">
         <x:v>-150</x:v>
       </x:c>
-      <x:c r="L15" s="0">
+      <x:c r="L15">
         <x:v>-80</x:v>
       </x:c>
-      <x:c r="M15" s="0">
+      <x:c r="M15">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="N15" s="0">
+      <x:c r="N15">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="O15" s="0">
+      <x:c r="O15">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="P15" s="0">
+      <x:c r="P15">
         <x:v>-43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
       <x:c r="A16" s="1"/>
-      <x:c r="C16" s="0">
+      <x:c r="C16">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D16" s="0">
+      <x:c r="D16">
         <x:v>-121</x:v>
       </x:c>
-      <x:c r="E16" s="0">
+      <x:c r="E16">
         <x:v>-153</x:v>
       </x:c>
-      <x:c r="F16" s="0">
+      <x:c r="F16">
         <x:v>-45</x:v>
       </x:c>
-      <x:c r="G16" s="0">
+      <x:c r="G16">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H16" s="0">
+      <x:c r="H16">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="I16" s="0">
+      <x:c r="I16">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="J16" s="0">
+      <x:c r="J16">
         <x:v>-87</x:v>
       </x:c>
-      <x:c r="K16" s="0">
+      <x:c r="K16">
         <x:v>-160</x:v>
       </x:c>
-      <x:c r="L16" s="0">
+      <x:c r="L16">
         <x:v>-86</x:v>
       </x:c>
-      <x:c r="M16" s="0">
+      <x:c r="M16">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="N16" s="0">
+      <x:c r="N16">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="O16" s="0">
+      <x:c r="O16">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="P16" s="0">
+      <x:c r="P16">
         <x:v>-46</x:v>
       </x:c>
     </x:row>
@@ -3270,136 +3246,136 @@
       <x:c r="A17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C17" s="0">
+      <x:c r="C17">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D17" s="0">
+      <x:c r="D17">
         <x:v>-129</x:v>
       </x:c>
-      <x:c r="E17" s="0">
+      <x:c r="E17">
         <x:v>-163</x:v>
       </x:c>
-      <x:c r="F17" s="0">
+      <x:c r="F17">
         <x:v>-48</x:v>
       </x:c>
-      <x:c r="G17" s="0">
+      <x:c r="G17">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H17" s="0">
+      <x:c r="H17">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="I17" s="0">
+      <x:c r="I17">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="J17" s="0">
+      <x:c r="J17">
         <x:v>-92</x:v>
       </x:c>
-      <x:c r="K17" s="0">
+      <x:c r="K17">
         <x:v>-170</x:v>
       </x:c>
-      <x:c r="L17" s="0">
+      <x:c r="L17">
         <x:v>-91</x:v>
       </x:c>
-      <x:c r="M17" s="0">
+      <x:c r="M17">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="N17" s="0">
+      <x:c r="N17">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="O17" s="0">
+      <x:c r="O17">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="P17" s="0">
+      <x:c r="P17">
         <x:v>-49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
       <x:c r="A18" s="1"/>
-      <x:c r="C18" s="0">
+      <x:c r="C18">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D18" s="0">
+      <x:c r="D18">
         <x:v>-136</x:v>
       </x:c>
-      <x:c r="E18" s="0">
+      <x:c r="E18">
         <x:v>-173</x:v>
       </x:c>
-      <x:c r="F18" s="0">
+      <x:c r="F18">
         <x:v>-50</x:v>
       </x:c>
-      <x:c r="G18" s="0">
+      <x:c r="G18">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="H18" s="0">
+      <x:c r="H18">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="I18" s="0">
+      <x:c r="I18">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="J18" s="0">
+      <x:c r="J18">
         <x:v>-98</x:v>
       </x:c>
-      <x:c r="K18" s="0">
+      <x:c r="K18">
         <x:v>-180</x:v>
       </x:c>
-      <x:c r="L18" s="0">
+      <x:c r="L18">
         <x:v>-97</x:v>
       </x:c>
-      <x:c r="M18" s="0">
+      <x:c r="M18">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="N18" s="0">
+      <x:c r="N18">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="O18" s="0">
+      <x:c r="O18">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="P18" s="0">
+      <x:c r="P18">
         <x:v>-52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
       <x:c r="A19" s="1"/>
-      <x:c r="C19" s="0">
+      <x:c r="C19">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D19" s="0">
+      <x:c r="D19">
         <x:v>-144</x:v>
       </x:c>
-      <x:c r="E19" s="0">
+      <x:c r="E19">
         <x:v>-182</x:v>
       </x:c>
-      <x:c r="F19" s="0">
+      <x:c r="F19">
         <x:v>-53</x:v>
       </x:c>
-      <x:c r="G19" s="0">
+      <x:c r="G19">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H19" s="0">
+      <x:c r="H19">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="I19" s="0">
+      <x:c r="I19">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="J19" s="0">
+      <x:c r="J19">
         <x:v>-103</x:v>
       </x:c>
-      <x:c r="K19" s="0">
+      <x:c r="K19">
         <x:v>-190</x:v>
       </x:c>
-      <x:c r="L19" s="0">
+      <x:c r="L19">
         <x:v>-102</x:v>
       </x:c>
-      <x:c r="M19" s="0">
+      <x:c r="M19">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N19" s="0">
+      <x:c r="N19">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="O19" s="0">
+      <x:c r="O19">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="P19" s="0">
+      <x:c r="P19">
         <x:v>-55</x:v>
       </x:c>
     </x:row>
@@ -3412,22 +3388,11 @@
     <x:mergeCell ref="A14:A16"/>
     <x:mergeCell ref="A17:A19"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="stacked" dateAxis="0" displayEmptyCellsAs="span" markers="1" high="1" low="1" first="1" last="1" negative="1" displayXAxis="0" displayHidden="0" minAxisType="group" maxAxisType="group" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="stacked" displayEmptyCellsAs="span" markers="1" high="1" low="1" first="1" last="1" negative="1" minAxisType="group" maxAxisType="group" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5F5F5F"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -3451,7 +3416,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="stacked" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="1" low="1" first="1" last="1" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="stacked" displayEmptyCellsAs="span" high="1" low="1" first="1" last="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5687C2"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -3475,7 +3440,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" manualMax="100" manualMin="-80" lineWeight="0.75" type="stacked" dateAxis="0" displayEmptyCellsAs="span" markers="1" high="0" low="0" first="0" last="0" negative="1" displayXAxis="0" displayHidden="0" minAxisType="custom" maxAxisType="custom" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" manualMax="100" manualMin="-80" type="stacked" displayEmptyCellsAs="span" markers="1" negative="1" minAxisType="custom" maxAxisType="custom" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FFC6EFCE"/>
           <x14:colorNegative rgb="FFFFC7CE"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -3499,7 +3464,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="stacked" dateAxis="1" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="0" last="0" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="stacked" dateAxis="1" displayEmptyCellsAs="span" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF5F5F5F"/>
           <x14:colorNegative rgb="FFFFB620"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -3524,7 +3489,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="2" type="stacked" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="0" last="0" negative="0" displayXAxis="1" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="2" type="stacked" displayEmptyCellsAs="span" displayXAxis="1" rightToLeft="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FF00B050"/>
           <x14:colorNegative rgb="FFFF0000"/>
           <x14:colorAxis rgb="FFFF0000"/>
@@ -3548,7 +3513,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" lineWeight="0.75" type="stacked" dateAxis="0" displayEmptyCellsAs="span" markers="0" high="0" low="0" first="1" last="1" negative="0" displayXAxis="0" displayHidden="0" minAxisType="individual" maxAxisType="individual" rightToLeft="0" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
+        <x14:sparklineGroup xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" type="stacked" displayEmptyCellsAs="span" first="1" last="1" xr2:uid="{A98FF5F8-AE60-43B5-8001-AD89004F45D3}">
           <x14:colorSeries rgb="FFC6EFCE"/>
           <x14:colorNegative rgb="FFFFC7CE"/>
           <x14:colorAxis rgb="FF000000"/>

--- a/XLibur.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
+++ b/XLibur.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
@@ -431,8 +431,8 @@
   <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="30.710625" customWidth="1"/>
+    <x:col min="1" max="1" width="30.714286" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="30.714286" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -1470,8 +1470,8 @@
   <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="30.710625" customWidth="1"/>
+    <x:col min="1" max="1" width="30.714286" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="30.714286" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16">
@@ -2509,8 +2509,8 @@
   <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="30.710625" customWidth="1"/>
+    <x:col min="1" max="1" width="30.714286" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="30.714286" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:16">
